--- a/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
     <sheet name="Router" sheetId="2" r:id="rId2"/>
+    <sheet name="公共服" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -78,52 +79,67 @@
     <t>外网端口</t>
   </si>
   <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>Gate1</t>
+  </si>
+  <si>
+    <t>Gate2</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>Map1</t>
+  </si>
+  <si>
+    <t>Map2</t>
+  </si>
+  <si>
+    <t>Game</t>
+  </si>
+  <si>
+    <t>Chat</t>
+  </si>
+  <si>
+    <t>UnitCache</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Mail</t>
+  </si>
+  <si>
+    <t>RouterManager</t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>Router01</t>
+  </si>
+  <si>
+    <t>Router02</t>
+  </si>
+  <si>
+    <t>Router03</t>
+  </si>
+  <si>
+    <t>Router04</t>
+  </si>
+  <si>
+    <t>LoginCenter</t>
+  </si>
+  <si>
     <t>Realm</t>
-  </si>
-  <si>
-    <t>Gate</t>
-  </si>
-  <si>
-    <t>Gate1</t>
-  </si>
-  <si>
-    <t>Gate2</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Match</t>
-  </si>
-  <si>
-    <t>Map</t>
-  </si>
-  <si>
-    <t>Map1</t>
-  </si>
-  <si>
-    <t>Map2</t>
-  </si>
-  <si>
-    <t>Map3</t>
-  </si>
-  <si>
-    <t>RouterManager</t>
-  </si>
-  <si>
-    <t>Router</t>
-  </si>
-  <si>
-    <t>Router01</t>
-  </si>
-  <si>
-    <t>Router02</t>
-  </si>
-  <si>
-    <t>Router03</t>
-  </si>
-  <si>
-    <t>Router04</t>
   </si>
 </sst>
 </file>
@@ -136,7 +152,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,12 +173,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -619,52 +629,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -673,83 +683,83 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
@@ -762,10 +772,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1117,19 +1124,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelCol="7"/>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.1296296296296" style="6" customWidth="1"/>
-    <col min="2" max="2" width="12.6296296296296" style="6" customWidth="1"/>
-    <col min="3" max="4" width="12.6296296296296" style="7" customWidth="1"/>
-    <col min="5" max="5" width="14.6296296296296" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13.3796296296296" style="7" customWidth="1"/>
-    <col min="7" max="8" width="13.1296296296296" style="7" customWidth="1"/>
+    <col min="1" max="1" width="21.125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="7" customWidth="1"/>
+    <col min="7" max="8" width="13.125" style="7" customWidth="1"/>
     <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.4" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="16.8" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1153,7 +1160,7 @@
       </c>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="14.4" spans="1:8">
+    <row r="2" s="2" customFormat="1" ht="16.8" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -1177,7 +1184,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="14.4" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="16.8" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1201,49 +1208,49 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
+    <row r="4" spans="1:8">
+      <c r="B4" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="7">
+        <v>40003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="5">
-        <v>30002</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="5">
-        <v>2</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="5">
-        <v>30003</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
+      <c r="G5" s="7">
+        <v>40004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="B6" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -1251,19 +1258,16 @@
       <c r="D6" s="5">
         <v>1</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="5">
-        <v>30004</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7">
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
@@ -1271,17 +1275,16 @@
       <c r="D7" s="5">
         <v>1</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="2:7">
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5">
         <v>1</v>
@@ -1289,35 +1292,33 @@
       <c r="D8" s="5">
         <v>1</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="5">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="5">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="2:7">
+    </row>
+    <row r="10" spans="1:8">
       <c r="B10" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
@@ -1325,17 +1326,16 @@
       <c r="D10" s="5">
         <v>1</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="2:6">
+    </row>
+    <row r="11" spans="1:8">
       <c r="B11" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -1343,11 +1343,62 @@
       <c r="D11" s="5">
         <v>1</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>25</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="5">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" s="5">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14" s="5">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1361,11 +1412,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="7.25" customWidth="1"/>
-    <col min="4" max="4" width="7.12962962962963" customWidth="1"/>
-    <col min="5" max="6" width="13.3796296296296" customWidth="1"/>
+    <col min="4" max="4" width="7.125" customWidth="1"/>
+    <col min="5" max="6" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -1440,7 +1491,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="1:8">
       <c r="B4" s="5">
         <v>300</v>
       </c>
@@ -1451,16 +1502,16 @@
         <v>3</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4" s="5">
         <v>30300</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="1:8">
       <c r="B5" s="5">
         <v>301</v>
       </c>
@@ -1471,16 +1522,16 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5" s="5">
         <v>30301</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="1:8">
       <c r="B6" s="5">
         <v>302</v>
       </c>
@@ -1491,16 +1542,16 @@
         <v>3</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G6" s="5">
         <v>30302</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="1:8">
       <c r="B7" s="5">
         <v>303</v>
       </c>
@@ -1511,16 +1562,16 @@
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G7" s="5">
         <v>30303</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="1:8">
       <c r="B8" s="5">
         <v>304</v>
       </c>
@@ -1531,10 +1582,10 @@
         <v>3</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G8" s="5">
         <v>30304</v>
@@ -1544,4 +1595,122 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="6"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="B4">
+        <v>401</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5">
+        <v>402</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5">
+        <v>40002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>